--- a/config/default/forms/app/pregnancy_facility_visit_reminder.xlsx
+++ b/config/default/forms/app/pregnancy_facility_visit_reminder.xlsx
@@ -1,15 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\apoorva\cht-core\config\default\forms\app\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E65DA76D-4DB4-48A6-A43B-33A95213F177}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="survey" sheetId="1" r:id="rId3"/>
-    <sheet state="visible" name="choices" sheetId="2" r:id="rId4"/>
-    <sheet state="visible" name="settings" sheetId="3" r:id="rId5"/>
-    <sheet state="hidden" name="choices-backup" sheetId="4" r:id="rId6"/>
+    <sheet name="survey" sheetId="1" r:id="rId1"/>
+    <sheet name="choices" sheetId="2" r:id="rId2"/>
+    <sheet name="settings" sheetId="3" r:id="rId3"/>
+    <sheet name="choices-backup" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -232,18 +252,12 @@
     <t>contact</t>
   </si>
   <si>
-    <t>db:person</t>
-  </si>
-  <si>
     <t>_id</t>
   </si>
   <si>
     <t>What is the patient's name?</t>
   </si>
   <si>
-    <t>db-object</t>
-  </si>
-  <si>
     <t>Name</t>
   </si>
   <si>
@@ -749,62 +763,74 @@
   </si>
   <si>
     <t>Pregnancy UUID</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>select-contact type-person</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd-MM-yyyy HH-mm-ss"/>
+    <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy\ hh\-mm\-ss"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
-    <font/>
     <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF76A5AF"/>
       <name val="Arial"/>
     </font>
@@ -814,7 +840,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -902,216 +928,471 @@
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="65">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="6" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="7" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="8" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="top"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="9" fontId="7" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="10" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="10" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="9" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="10" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="11" fontId="7" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="12" fontId="7" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="12" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="12" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="11" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="12" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="12" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="13" fontId="7" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="13" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="8" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="8" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="14" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="8" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="8" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="15" fontId="7" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="7" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="7" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="7" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="15" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="15" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="7" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="7" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="7" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <dimension ref="A1:AJ55"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="19.0"/>
-    <col customWidth="1" min="2" max="2" width="33.29"/>
-    <col customWidth="1" min="3" max="3" width="43.29"/>
-    <col customWidth="1" hidden="1" min="4" max="5" width="8.57"/>
-    <col customWidth="1" hidden="1" min="6" max="6" width="8.71"/>
-    <col customWidth="1" hidden="1" min="7" max="7" width="8.86"/>
-    <col customWidth="1" hidden="1" min="8" max="9" width="8.14"/>
-    <col customWidth="1" min="10" max="10" width="14.43"/>
-    <col customWidth="1" min="11" max="11" width="53.86"/>
-    <col customWidth="1" min="12" max="12" width="17.43"/>
-    <col customWidth="1" min="13" max="13" width="37.71"/>
-    <col customWidth="1" min="14" max="14" width="32.71"/>
-    <col customWidth="1" hidden="1" min="15" max="20" width="25.86"/>
-    <col customWidth="1" min="21" max="21" width="73.86"/>
-    <col customWidth="1" min="22" max="22" width="14.43"/>
-    <col customWidth="1" min="23" max="23" width="30.0"/>
-    <col customWidth="1" hidden="1" min="24" max="29" width="14.43"/>
-    <col customWidth="1" min="30" max="30" width="14.43"/>
-    <col customWidth="1" min="31" max="36" width="29.86"/>
+    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="2" max="2" width="33.33203125" customWidth="1"/>
+    <col min="3" max="3" width="43.33203125" customWidth="1"/>
+    <col min="4" max="5" width="8.5546875" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="8.6640625" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" hidden="1" customWidth="1"/>
+    <col min="8" max="9" width="8.109375" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="14.44140625" customWidth="1"/>
+    <col min="11" max="11" width="53.88671875" customWidth="1"/>
+    <col min="12" max="12" width="22.77734375" customWidth="1"/>
+    <col min="13" max="13" width="37.6640625" customWidth="1"/>
+    <col min="14" max="14" width="32.6640625" customWidth="1"/>
+    <col min="15" max="20" width="25.88671875" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="73.88671875" customWidth="1"/>
+    <col min="22" max="22" width="14.44140625" customWidth="1"/>
+    <col min="23" max="23" width="30" customWidth="1"/>
+    <col min="24" max="29" width="14.44140625" hidden="1" customWidth="1"/>
+    <col min="30" max="30" width="14.44140625" customWidth="1"/>
+    <col min="31" max="36" width="29.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
+    <row r="1" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1217,7 +1498,7 @@
       <c r="AI1" s="14"/>
       <c r="AJ1" s="14"/>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
+    <row r="2" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>45</v>
       </c>
@@ -1265,7 +1546,7 @@
       <c r="AI2" s="26"/>
       <c r="AJ2" s="26"/>
     </row>
-    <row r="3" ht="15.75" customHeight="1">
+    <row r="3" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>60</v>
       </c>
@@ -1311,7 +1592,7 @@
       <c r="AI3" s="26"/>
       <c r="AJ3" s="26"/>
     </row>
-    <row r="4" ht="15.75" customHeight="1">
+    <row r="4" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
         <v>60</v>
       </c>
@@ -1355,7 +1636,7 @@
       <c r="AI4" s="26"/>
       <c r="AJ4" s="26"/>
     </row>
-    <row r="5" ht="15.75" customHeight="1">
+    <row r="5" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="28" t="s">
         <v>60</v>
       </c>
@@ -1399,7 +1680,7 @@
       <c r="AI5" s="26"/>
       <c r="AJ5" s="26"/>
     </row>
-    <row r="6" ht="15.75" customHeight="1">
+    <row r="6" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>45</v>
       </c>
@@ -1443,15 +1724,15 @@
       <c r="AI6" s="26"/>
       <c r="AJ6" s="26"/>
     </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="16" t="s">
+    <row r="7" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="63" t="s">
+        <v>243</v>
+      </c>
+      <c r="B7" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="C7" s="23" t="s">
         <v>73</v>
-      </c>
-      <c r="C7" s="23" t="s">
-        <v>74</v>
       </c>
       <c r="D7" s="23"/>
       <c r="E7" s="23"/>
@@ -1461,8 +1742,8 @@
       <c r="I7" s="23"/>
       <c r="J7" s="23"/>
       <c r="K7" s="23"/>
-      <c r="L7" s="23" t="s">
-        <v>75</v>
+      <c r="L7" s="64" t="s">
+        <v>244</v>
       </c>
       <c r="M7" s="23"/>
       <c r="N7" s="23"/>
@@ -1489,7 +1770,7 @@
       <c r="AI7" s="26"/>
       <c r="AJ7" s="26"/>
     </row>
-    <row r="8" ht="15.75" customHeight="1">
+    <row r="8" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
         <v>60</v>
       </c>
@@ -1497,7 +1778,7 @@
         <v>3</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D8" s="23"/>
       <c r="E8" s="23"/>
@@ -1533,15 +1814,15 @@
       <c r="AI8" s="26"/>
       <c r="AJ8" s="26"/>
     </row>
-    <row r="9" ht="15.75" customHeight="1">
+    <row r="9" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="28" t="s">
         <v>60</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D9" s="23"/>
       <c r="E9" s="23"/>
@@ -1577,15 +1858,15 @@
       <c r="AI9" s="26"/>
       <c r="AJ9" s="26"/>
     </row>
-    <row r="10" ht="15.75" customHeight="1">
+    <row r="10" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
         <v>60</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D10" s="23"/>
       <c r="E10" s="23"/>
@@ -1621,15 +1902,15 @@
       <c r="AI10" s="26"/>
       <c r="AJ10" s="26"/>
     </row>
-    <row r="11" ht="15.75" customHeight="1">
+    <row r="11" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
         <v>60</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D11" s="23"/>
       <c r="E11" s="23"/>
@@ -1658,7 +1939,7 @@
       <c r="AB11" s="23"/>
       <c r="AC11" s="23"/>
       <c r="AD11" s="23">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="AE11" s="23"/>
       <c r="AF11" s="23"/>
@@ -1667,15 +1948,15 @@
       <c r="AI11" s="26"/>
       <c r="AJ11" s="26"/>
     </row>
-    <row r="12" ht="15.75" customHeight="1">
+    <row r="12" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
         <v>60</v>
       </c>
       <c r="B12" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" s="23" t="s">
         <v>100</v>
-      </c>
-      <c r="C12" s="23" t="s">
-        <v>102</v>
       </c>
       <c r="D12" s="23"/>
       <c r="E12" s="23"/>
@@ -1711,12 +1992,12 @@
       <c r="AI12" s="26"/>
       <c r="AJ12" s="26"/>
     </row>
-    <row r="13" ht="15.75" customHeight="1">
+    <row r="13" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
         <v>45</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C13" s="21" t="s">
         <v>49</v>
@@ -1755,15 +2036,15 @@
       <c r="AI13" s="26"/>
       <c r="AJ13" s="26"/>
     </row>
-    <row r="14" ht="15.75" customHeight="1">
+    <row r="14" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
         <v>60</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D14" s="23"/>
       <c r="E14" s="23"/>
@@ -1799,12 +2080,12 @@
       <c r="AI14" s="30"/>
       <c r="AJ14" s="30"/>
     </row>
-    <row r="15" ht="15.75" customHeight="1">
+    <row r="15" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
         <v>45</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C15" s="21" t="s">
         <v>49</v>
@@ -1843,7 +2124,7 @@
       <c r="AI15" s="26"/>
       <c r="AJ15" s="26"/>
     </row>
-    <row r="16" ht="15.75" customHeight="1">
+    <row r="16" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
         <v>45</v>
       </c>
@@ -1887,15 +2168,15 @@
       <c r="AI16" s="26"/>
       <c r="AJ16" s="26"/>
     </row>
-    <row r="17" ht="15.75" customHeight="1">
+    <row r="17" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
         <v>60</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D17" s="23"/>
       <c r="E17" s="23"/>
@@ -1931,15 +2212,15 @@
       <c r="AI17" s="26"/>
       <c r="AJ17" s="26"/>
     </row>
-    <row r="18" ht="15.75" customHeight="1">
+    <row r="18" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
         <v>60</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D18" s="23"/>
       <c r="E18" s="23"/>
@@ -1975,9 +2256,9 @@
       <c r="AI18" s="26"/>
       <c r="AJ18" s="26"/>
     </row>
-    <row r="19" ht="15.75" customHeight="1">
+    <row r="19" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B19" s="28" t="s">
         <v>71</v>
@@ -2017,12 +2298,12 @@
       <c r="AI19" s="26"/>
       <c r="AJ19" s="26"/>
     </row>
-    <row r="20" ht="15.75" customHeight="1">
+    <row r="20" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B20" s="28" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C20" s="23"/>
       <c r="D20" s="23"/>
@@ -2059,12 +2340,12 @@
       <c r="AI20" s="26"/>
       <c r="AJ20" s="26"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
+    <row r="21" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B21" s="28" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C21" s="23"/>
       <c r="D21" s="23"/>
@@ -2101,9 +2382,9 @@
       <c r="AI21" s="26"/>
       <c r="AJ21" s="26"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
+    <row r="22" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B22" s="28" t="s">
         <v>71</v>
@@ -2143,9 +2424,9 @@
       <c r="AI22" s="26"/>
       <c r="AJ22" s="26"/>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
+    <row r="23" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B23" s="28" t="s">
         <v>48</v>
@@ -2187,7 +2468,7 @@
       <c r="AI23" s="26"/>
       <c r="AJ23" s="26"/>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
+    <row r="24" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="31"/>
       <c r="B24" s="31"/>
       <c r="C24" s="31"/>
@@ -2225,12 +2506,12 @@
       <c r="AI24" s="33"/>
       <c r="AJ24" s="33"/>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
+    <row r="25" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="34" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B25" s="34" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C25" s="35" t="s">
         <v>49</v>
@@ -2253,7 +2534,7 @@
       <c r="S25" s="35"/>
       <c r="T25" s="35"/>
       <c r="U25" s="35" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="V25" s="35"/>
       <c r="W25" s="35"/>
@@ -2273,12 +2554,12 @@
       <c r="AI25" s="37"/>
       <c r="AJ25" s="37"/>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
+    <row r="26" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="34" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B26" s="34" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C26" s="35" t="s">
         <v>49</v>
@@ -2301,7 +2582,7 @@
       <c r="S26" s="35"/>
       <c r="T26" s="35"/>
       <c r="U26" s="35" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="V26" s="35"/>
       <c r="W26" s="35"/>
@@ -2321,12 +2602,12 @@
       <c r="AI26" s="37"/>
       <c r="AJ26" s="37"/>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
+    <row r="27" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="34" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B27" s="34" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C27" s="35" t="s">
         <v>49</v>
@@ -2349,7 +2630,7 @@
       <c r="S27" s="35"/>
       <c r="T27" s="35"/>
       <c r="U27" s="36" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="V27" s="35"/>
       <c r="W27" s="35"/>
@@ -2369,12 +2650,12 @@
       <c r="AI27" s="37"/>
       <c r="AJ27" s="37"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
+    <row r="28" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="34" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B28" s="34" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C28" s="35" t="s">
         <v>49</v>
@@ -2397,7 +2678,7 @@
       <c r="S28" s="35"/>
       <c r="T28" s="35"/>
       <c r="U28" s="36" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="V28" s="35"/>
       <c r="W28" s="35"/>
@@ -2417,12 +2698,12 @@
       <c r="AI28" s="37"/>
       <c r="AJ28" s="37"/>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
+    <row r="29" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="38" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C29" s="36" t="s">
         <v>49</v>
@@ -2445,7 +2726,7 @@
       <c r="S29" s="35"/>
       <c r="T29" s="35"/>
       <c r="U29" s="36" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="V29" s="35"/>
       <c r="W29" s="35"/>
@@ -2465,12 +2746,12 @@
       <c r="AI29" s="37"/>
       <c r="AJ29" s="37"/>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
+    <row r="30" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="34" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C30" s="36" t="s">
         <v>49</v>
@@ -2493,7 +2774,7 @@
       <c r="S30" s="35"/>
       <c r="T30" s="35"/>
       <c r="U30" s="36" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="V30" s="35"/>
       <c r="W30" s="35"/>
@@ -2513,12 +2794,12 @@
       <c r="AI30" s="37"/>
       <c r="AJ30" s="37"/>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
+    <row r="31" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="34" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B31" s="38" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C31" s="36" t="s">
         <v>49</v>
@@ -2541,7 +2822,7 @@
       <c r="S31" s="35"/>
       <c r="T31" s="35"/>
       <c r="U31" s="35" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="V31" s="35"/>
       <c r="W31" s="35"/>
@@ -2559,12 +2840,12 @@
       <c r="AI31" s="39"/>
       <c r="AJ31" s="39"/>
     </row>
-    <row r="32" ht="15.75" customHeight="1">
+    <row r="32" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="38" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B32" s="38" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C32" s="36" t="s">
         <v>49</v>
@@ -2587,7 +2868,7 @@
       <c r="S32" s="35"/>
       <c r="T32" s="35"/>
       <c r="U32" s="36" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="V32" s="35"/>
       <c r="W32" s="35"/>
@@ -2605,7 +2886,7 @@
       <c r="AI32" s="39"/>
       <c r="AJ32" s="39"/>
     </row>
-    <row r="33" ht="15.75" customHeight="1">
+    <row r="33" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="31"/>
       <c r="B33" s="32"/>
       <c r="C33" s="32"/>
@@ -2643,15 +2924,15 @@
       <c r="AI33" s="41"/>
       <c r="AJ33" s="41"/>
     </row>
-    <row r="34" ht="15.75" customHeight="1">
+    <row r="34" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="42" t="s">
         <v>45</v>
       </c>
       <c r="B34" s="43" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C34" s="44" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D34" s="45"/>
       <c r="E34" s="45"/>
@@ -2689,15 +2970,15 @@
       <c r="AI34" s="47"/>
       <c r="AJ34" s="47"/>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
+    <row r="35" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="43" t="s">
+        <v>206</v>
+      </c>
+      <c r="B35" s="43" t="s">
+        <v>207</v>
+      </c>
+      <c r="C35" s="44" t="s">
         <v>208</v>
-      </c>
-      <c r="B35" s="43" t="s">
-        <v>209</v>
-      </c>
-      <c r="C35" s="44" t="s">
-        <v>210</v>
       </c>
       <c r="D35" s="45"/>
       <c r="E35" s="45"/>
@@ -2735,15 +3016,15 @@
       <c r="AI35" s="47"/>
       <c r="AJ35" s="47"/>
     </row>
-    <row r="36" ht="15.75" customHeight="1">
+    <row r="36" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="43" t="s">
+        <v>209</v>
+      </c>
+      <c r="B36" s="43" t="s">
+        <v>210</v>
+      </c>
+      <c r="C36" s="44" t="s">
         <v>211</v>
-      </c>
-      <c r="B36" s="43" t="s">
-        <v>212</v>
-      </c>
-      <c r="C36" s="44" t="s">
-        <v>213</v>
       </c>
       <c r="D36" s="45"/>
       <c r="E36" s="45"/>
@@ -2779,12 +3060,12 @@
       <c r="AI36" s="47"/>
       <c r="AJ36" s="47"/>
     </row>
-    <row r="37" ht="15.75" customHeight="1">
+    <row r="37" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="43" t="s">
         <v>45</v>
       </c>
       <c r="B37" s="43" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C37" s="44" t="s">
         <v>49</v>
@@ -2827,12 +3108,12 @@
       <c r="AI37" s="48"/>
       <c r="AJ37" s="48"/>
     </row>
-    <row r="38" ht="15.75" customHeight="1">
+    <row r="38" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="43" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B38" s="43" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C38" s="45" t="s">
         <v>49</v>
@@ -2855,7 +3136,7 @@
       <c r="S38" s="45"/>
       <c r="T38" s="45"/>
       <c r="U38" s="44" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="V38" s="45"/>
       <c r="W38" s="45"/>
@@ -2873,12 +3154,12 @@
       <c r="AI38" s="48"/>
       <c r="AJ38" s="48"/>
     </row>
-    <row r="39" ht="15.75" customHeight="1">
+    <row r="39" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="43" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B39" s="43" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C39" s="45" t="s">
         <v>49</v>
@@ -2901,7 +3182,7 @@
       <c r="S39" s="45"/>
       <c r="T39" s="45"/>
       <c r="U39" s="44" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="V39" s="45"/>
       <c r="W39" s="45"/>
@@ -2919,12 +3200,12 @@
       <c r="AI39" s="48"/>
       <c r="AJ39" s="48"/>
     </row>
-    <row r="40" ht="15.75" customHeight="1">
+    <row r="40" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="43" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B40" s="43" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C40" s="45" t="s">
         <v>49</v>
@@ -2947,7 +3228,7 @@
       <c r="S40" s="45"/>
       <c r="T40" s="45"/>
       <c r="U40" s="44" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="V40" s="45"/>
       <c r="W40" s="45"/>
@@ -2965,12 +3246,12 @@
       <c r="AI40" s="48"/>
       <c r="AJ40" s="48"/>
     </row>
-    <row r="41" ht="15.75" customHeight="1">
+    <row r="41" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="43" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B41" s="43" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C41" s="45" t="s">
         <v>49</v>
@@ -2993,7 +3274,7 @@
       <c r="S41" s="45"/>
       <c r="T41" s="45"/>
       <c r="U41" s="44" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="V41" s="45"/>
       <c r="W41" s="45"/>
@@ -3011,9 +3292,9 @@
       <c r="AI41" s="48"/>
       <c r="AJ41" s="48"/>
     </row>
-    <row r="42" ht="15.75" customHeight="1">
+    <row r="42" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="43" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B42" s="42"/>
       <c r="C42" s="44"/>
@@ -3051,9 +3332,9 @@
       <c r="AI42" s="49"/>
       <c r="AJ42" s="49"/>
     </row>
-    <row r="43" ht="15.75" customHeight="1">
+    <row r="43" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="42" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B43" s="42"/>
       <c r="C43" s="44"/>
@@ -3091,7 +3372,7 @@
       <c r="AI43" s="49"/>
       <c r="AJ43" s="49"/>
     </row>
-    <row r="44" ht="15.75" customHeight="1">
+    <row r="44" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="32"/>
       <c r="B44" s="32"/>
       <c r="C44" s="32"/>
@@ -3129,7 +3410,7 @@
       <c r="AI44" s="50"/>
       <c r="AJ44" s="50"/>
     </row>
-    <row r="45" ht="15.75" customHeight="1">
+    <row r="45" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="51" t="s">
         <v>45</v>
       </c>
@@ -3177,12 +3458,12 @@
       <c r="AI45" s="56"/>
       <c r="AJ45" s="56"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1">
+    <row r="46" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="51" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B46" s="57" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C46" s="52" t="s">
         <v>49</v>
@@ -3205,7 +3486,7 @@
       <c r="S46" s="53"/>
       <c r="T46" s="53"/>
       <c r="U46" s="52" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="V46" s="53"/>
       <c r="W46" s="53"/>
@@ -3220,17 +3501,17 @@
       <c r="AF46" s="52"/>
       <c r="AG46" s="52"/>
       <c r="AH46" s="58" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AI46" s="56"/>
       <c r="AJ46" s="56"/>
     </row>
-    <row r="47" ht="15.75" customHeight="1">
+    <row r="47" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="59" t="s">
         <v>45</v>
       </c>
       <c r="B47" s="59" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C47" s="52" t="s">
         <v>49</v>
@@ -3269,12 +3550,12 @@
       <c r="AI47" s="61"/>
       <c r="AJ47" s="61"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1">
+    <row r="48" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="51" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B48" s="57" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C48" s="52" t="s">
         <v>49</v>
@@ -3297,7 +3578,7 @@
       <c r="S48" s="53"/>
       <c r="T48" s="53"/>
       <c r="U48" s="61" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="V48" s="53"/>
       <c r="W48" s="53"/>
@@ -3312,17 +3593,17 @@
       <c r="AF48" s="52"/>
       <c r="AG48" s="52"/>
       <c r="AH48" s="61" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="AI48" s="56"/>
       <c r="AJ48" s="56"/>
     </row>
-    <row r="49" ht="15.75" customHeight="1">
+    <row r="49" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="51" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B49" s="57" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C49" s="52" t="s">
         <v>49</v>
@@ -3345,7 +3626,7 @@
       <c r="S49" s="53"/>
       <c r="T49" s="53"/>
       <c r="U49" s="61" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="V49" s="53"/>
       <c r="W49" s="53"/>
@@ -3360,17 +3641,17 @@
       <c r="AF49" s="52"/>
       <c r="AG49" s="52"/>
       <c r="AH49" s="61" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AI49" s="56"/>
       <c r="AJ49" s="56"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1">
+    <row r="50" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="51" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B50" s="57" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C50" s="52" t="s">
         <v>49</v>
@@ -3393,7 +3674,7 @@
       <c r="S50" s="53"/>
       <c r="T50" s="53"/>
       <c r="U50" s="61" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="V50" s="53"/>
       <c r="W50" s="53"/>
@@ -3408,17 +3689,17 @@
       <c r="AF50" s="52"/>
       <c r="AG50" s="52"/>
       <c r="AH50" s="62" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AI50" s="56"/>
       <c r="AJ50" s="56"/>
     </row>
-    <row r="51" ht="15.75" customHeight="1">
+    <row r="51" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="51" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B51" s="57" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C51" s="52" t="s">
         <v>49</v>
@@ -3441,7 +3722,7 @@
       <c r="S51" s="53"/>
       <c r="T51" s="53"/>
       <c r="U51" s="61" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="V51" s="53"/>
       <c r="W51" s="53"/>
@@ -3461,12 +3742,12 @@
       <c r="AI51" s="56"/>
       <c r="AJ51" s="56"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1">
+    <row r="52" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="51" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B52" s="57" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C52" s="52" t="s">
         <v>49</v>
@@ -3489,7 +3770,7 @@
       <c r="S52" s="53"/>
       <c r="T52" s="53"/>
       <c r="U52" s="61" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="V52" s="53"/>
       <c r="W52" s="53"/>
@@ -3504,17 +3785,17 @@
       <c r="AF52" s="52"/>
       <c r="AG52" s="52"/>
       <c r="AH52" s="61" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AI52" s="56"/>
       <c r="AJ52" s="56"/>
     </row>
-    <row r="53" ht="15.75" customHeight="1">
+    <row r="53" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="51" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B53" s="57" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C53" s="52" t="s">
         <v>49</v>
@@ -3537,7 +3818,7 @@
       <c r="S53" s="53"/>
       <c r="T53" s="53"/>
       <c r="U53" s="52" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="V53" s="53"/>
       <c r="W53" s="53"/>
@@ -3552,17 +3833,17 @@
       <c r="AF53" s="52"/>
       <c r="AG53" s="52"/>
       <c r="AH53" s="61" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="AI53" s="56"/>
       <c r="AJ53" s="56"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1">
+    <row r="54" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="59" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B54" s="59" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C54" s="55"/>
       <c r="D54" s="60"/>
@@ -3599,9 +3880,9 @@
       <c r="AI54" s="61"/>
       <c r="AJ54" s="61"/>
     </row>
-    <row r="55" ht="15.75" customHeight="1">
+    <row r="55" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="59" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B55" s="59" t="s">
         <v>53</v>
@@ -3642,27 +3923,28 @@
       <c r="AJ55" s="61"/>
     </row>
   </sheetData>
-  <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="J2:J55">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" sqref="J2:J55" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"yes,no"</formula1>
     </dataValidation>
   </dataValidations>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <dimension ref="A1:V67"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="28.29"/>
-    <col customWidth="1" min="2" max="22" width="45.86"/>
+    <col min="1" max="1" width="28.33203125" customWidth="1"/>
+    <col min="2" max="22" width="45.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
+    <row r="1" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -3704,7 +3986,7 @@
       <c r="U1" s="13"/>
       <c r="V1" s="13"/>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
+    <row r="2" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
         <v>44</v>
       </c>
@@ -3734,7 +4016,7 @@
       <c r="U2" s="19"/>
       <c r="V2" s="19"/>
     </row>
-    <row r="3" ht="15.75" customHeight="1">
+    <row r="3" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
         <v>44</v>
       </c>
@@ -3764,7 +4046,7 @@
       <c r="U3" s="19"/>
       <c r="V3" s="19"/>
     </row>
-    <row r="4" ht="15.75" customHeight="1">
+    <row r="4" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="24"/>
@@ -3788,7 +4070,7 @@
       <c r="U4" s="19"/>
       <c r="V4" s="19"/>
     </row>
-    <row r="5" ht="15.75" customHeight="1">
+    <row r="5" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="25" t="s">
         <v>57</v>
       </c>
@@ -3799,7 +4081,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" ht="15.75" customHeight="1">
+    <row r="6" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="25" t="s">
         <v>63</v>
       </c>
@@ -3810,208 +4092,209 @@
         <v>65</v>
       </c>
     </row>
-    <row r="7" ht="15.75" customHeight="1">
+    <row r="7" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" s="19"/>
     </row>
-    <row r="8" ht="15.75" customHeight="1">
+    <row r="8" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C8" s="19"/>
     </row>
-    <row r="9" ht="15.75" customHeight="1">
+    <row r="9" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C9" s="19"/>
     </row>
-    <row r="10" ht="15.75" customHeight="1">
+    <row r="10" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C10" s="19"/>
     </row>
-    <row r="11" ht="15.75" customHeight="1">
+    <row r="11" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C11" s="19"/>
     </row>
-    <row r="12" ht="15.75" customHeight="1">
+    <row r="12" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C12" s="19"/>
     </row>
-    <row r="13" ht="15.75" customHeight="1">
+    <row r="13" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C13" s="19"/>
     </row>
-    <row r="14" ht="15.75" customHeight="1">
+    <row r="14" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C14" s="19"/>
     </row>
-    <row r="15" ht="15.75" customHeight="1">
+    <row r="15" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C15" s="19"/>
     </row>
-    <row r="16" ht="15.75" customHeight="1">
+    <row r="16" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C16" s="19"/>
     </row>
-    <row r="17" ht="15.75" customHeight="1">
+    <row r="17" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C17" s="19"/>
     </row>
-    <row r="18" ht="15.75" customHeight="1">
+    <row r="18" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C18" s="19"/>
     </row>
-    <row r="19" ht="15.75" customHeight="1">
+    <row r="19" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C19" s="19"/>
     </row>
-    <row r="20" ht="15.75" customHeight="1">
+    <row r="20" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C20" s="19"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
+    <row r="21" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="19"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
+    <row r="22" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="19"/>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
+    <row r="23" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C23" s="19"/>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
+    <row r="24" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C24" s="19"/>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
+    <row r="25" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C25" s="19"/>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
+    <row r="26" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C26" s="19"/>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
+    <row r="27" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C27" s="19"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
+    <row r="28" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C28" s="19"/>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
+    <row r="29" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C29" s="19"/>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
+    <row r="30" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C30" s="19"/>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
+    <row r="31" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C31" s="19"/>
     </row>
-    <row r="32" ht="15.75" customHeight="1">
+    <row r="32" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C32" s="19"/>
     </row>
-    <row r="33" ht="15.75" customHeight="1">
+    <row r="33" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C33" s="19"/>
     </row>
-    <row r="34" ht="15.75" customHeight="1">
+    <row r="34" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C34" s="19"/>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
+    <row r="35" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C35" s="19"/>
     </row>
-    <row r="36" ht="15.75" customHeight="1">
+    <row r="36" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C36" s="19"/>
     </row>
-    <row r="37" ht="15.75" customHeight="1">
+    <row r="37" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C37" s="19"/>
     </row>
-    <row r="38" ht="15.75" customHeight="1">
+    <row r="38" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C38" s="19"/>
     </row>
-    <row r="39" ht="15.75" customHeight="1">
+    <row r="39" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C39" s="19"/>
     </row>
-    <row r="40" ht="15.75" customHeight="1">
+    <row r="40" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C40" s="19"/>
     </row>
-    <row r="41" ht="15.75" customHeight="1">
+    <row r="41" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C41" s="19"/>
     </row>
-    <row r="42" ht="15.75" customHeight="1">
+    <row r="42" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C42" s="19"/>
     </row>
-    <row r="43" ht="15.75" customHeight="1">
+    <row r="43" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C43" s="19"/>
     </row>
-    <row r="44" ht="15.75" customHeight="1">
+    <row r="44" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C44" s="19"/>
     </row>
-    <row r="45" ht="15.75" customHeight="1">
+    <row r="45" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C45" s="19"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1">
+    <row r="46" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C46" s="19"/>
     </row>
-    <row r="47" ht="15.75" customHeight="1">
+    <row r="47" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C47" s="19"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1">
+    <row r="48" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C48" s="19"/>
     </row>
-    <row r="49" ht="15.75" customHeight="1">
+    <row r="49" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C49" s="19"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1">
+    <row r="50" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C50" s="19"/>
     </row>
-    <row r="51" ht="15.75" customHeight="1">
+    <row r="51" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C51" s="19"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1">
+    <row r="52" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C52" s="19"/>
     </row>
-    <row r="53" ht="15.75" customHeight="1">
+    <row r="53" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C53" s="19"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1">
+    <row r="54" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C54" s="19"/>
     </row>
-    <row r="55" ht="15.75" customHeight="1">
+    <row r="55" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C55" s="19"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1">
+    <row r="56" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C56" s="19"/>
     </row>
-    <row r="57" ht="15.75" customHeight="1">
+    <row r="57" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C57" s="19"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1">
+    <row r="58" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C58" s="19"/>
     </row>
-    <row r="59" ht="15.75" customHeight="1">
+    <row r="59" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C59" s="19"/>
     </row>
-    <row r="60" ht="15.75" customHeight="1">
+    <row r="60" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C60" s="19"/>
     </row>
-    <row r="61" ht="15.75" customHeight="1">
+    <row r="61" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C61" s="19"/>
     </row>
-    <row r="62" ht="15.75" customHeight="1">
+    <row r="62" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C62" s="19"/>
     </row>
-    <row r="63" ht="15.75" customHeight="1">
+    <row r="63" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C63" s="19"/>
     </row>
-    <row r="64" ht="15.75" customHeight="1">
+    <row r="64" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C64" s="19"/>
     </row>
-    <row r="65" ht="15.75" customHeight="1">
+    <row r="65" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C65" s="19"/>
     </row>
-    <row r="66" ht="15.75" customHeight="1">
+    <row r="66" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C66" s="19"/>
     </row>
-    <row r="67" ht="15.75" customHeight="1">
+    <row r="67" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C67" s="19"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <dimension ref="A1:Z2"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="21.0"/>
-    <col customWidth="1" min="2" max="2" width="28.57"/>
-    <col customWidth="1" min="3" max="3" width="24.57"/>
-    <col customWidth="1" min="4" max="6" width="14.43"/>
+    <col min="1" max="1" width="21" customWidth="1"/>
+    <col min="2" max="2" width="28.5546875" customWidth="1"/>
+    <col min="3" max="3" width="24.5546875" customWidth="1"/>
+    <col min="4" max="6" width="14.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
+    <row r="1" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
@@ -4053,7 +4336,7 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
+    <row r="2" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>38</v>
       </c>
@@ -4061,8 +4344,8 @@
         <v>43</v>
       </c>
       <c r="C2" s="18">
-        <f>NOW()</f>
-        <v>43773.59398</v>
+        <f ca="1">NOW()</f>
+        <v>45778.936595023151</v>
       </c>
       <c r="D2" s="20" t="s">
         <v>50</v>
@@ -4095,22 +4378,23 @@
       <c r="Z2" s="13"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <dimension ref="A1:W1000"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="28.29"/>
-    <col customWidth="1" min="2" max="23" width="45.86"/>
+    <col min="1" max="1" width="28.33203125" customWidth="1"/>
+    <col min="2" max="23" width="45.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
+    <row r="1" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -4153,15 +4437,15 @@
       <c r="V1" s="13"/>
       <c r="W1" s="13"/>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
+    <row r="2" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" s="19" t="s">
         <v>77</v>
-      </c>
-      <c r="B2" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="C2" s="19" t="s">
-        <v>79</v>
       </c>
       <c r="D2" s="19"/>
       <c r="E2" s="19"/>
@@ -4184,15 +4468,15 @@
       <c r="V2" s="19"/>
       <c r="W2" s="19"/>
     </row>
-    <row r="3" ht="15.75" customHeight="1">
+    <row r="3" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D3" s="19"/>
       <c r="E3" s="19"/>
@@ -4215,7 +4499,7 @@
       <c r="V3" s="19"/>
       <c r="W3" s="19"/>
     </row>
-    <row r="4" ht="15.75" customHeight="1">
+    <row r="4" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="19"/>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -4240,15 +4524,15 @@
       <c r="V4" s="19"/>
       <c r="W4" s="19"/>
     </row>
-    <row r="5" ht="15.75" customHeight="1">
+    <row r="5" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" s="19" t="s">
         <v>84</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>86</v>
       </c>
       <c r="D5" s="19"/>
       <c r="E5" s="19"/>
@@ -4271,15 +4555,15 @@
       <c r="V5" s="19"/>
       <c r="W5" s="19"/>
     </row>
-    <row r="6" ht="15.75" customHeight="1">
+    <row r="6" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D6" s="19"/>
       <c r="E6" s="19"/>
@@ -4302,15 +4586,15 @@
       <c r="V6" s="19"/>
       <c r="W6" s="19"/>
     </row>
-    <row r="7" ht="15.75" customHeight="1">
+    <row r="7" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D7" s="19"/>
       <c r="E7" s="19"/>
@@ -4333,15 +4617,15 @@
       <c r="V7" s="19"/>
       <c r="W7" s="19"/>
     </row>
-    <row r="8" ht="15.75" customHeight="1">
+    <row r="8" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D8" s="19"/>
       <c r="E8" s="19"/>
@@ -4364,15 +4648,15 @@
       <c r="V8" s="19"/>
       <c r="W8" s="19"/>
     </row>
-    <row r="9" ht="15.75" customHeight="1">
+    <row r="9" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D9" s="19"/>
       <c r="E9" s="19"/>
@@ -4395,7 +4679,7 @@
       <c r="V9" s="19"/>
       <c r="W9" s="19"/>
     </row>
-    <row r="10" ht="15.75" customHeight="1">
+    <row r="10" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="19"/>
       <c r="B10" s="19"/>
       <c r="C10" s="19"/>
@@ -4420,15 +4704,15 @@
       <c r="V10" s="19"/>
       <c r="W10" s="19"/>
     </row>
-    <row r="11" ht="15.75" customHeight="1">
+    <row r="11" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="B11" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="C11" s="19" t="s">
         <v>101</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>103</v>
       </c>
       <c r="D11" s="19"/>
       <c r="E11" s="19"/>
@@ -4451,15 +4735,15 @@
       <c r="V11" s="19"/>
       <c r="W11" s="19"/>
     </row>
-    <row r="12" ht="15.75" customHeight="1">
+    <row r="12" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D12" s="19"/>
       <c r="E12" s="19"/>
@@ -4482,15 +4766,15 @@
       <c r="V12" s="19"/>
       <c r="W12" s="19"/>
     </row>
-    <row r="13" ht="15.75" customHeight="1">
+    <row r="13" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D13" s="19"/>
       <c r="E13" s="19"/>
@@ -4513,15 +4797,15 @@
       <c r="V13" s="19"/>
       <c r="W13" s="19"/>
     </row>
-    <row r="14" ht="15.75" customHeight="1">
+    <row r="14" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D14" s="19"/>
       <c r="E14" s="19"/>
@@ -4544,15 +4828,15 @@
       <c r="V14" s="19"/>
       <c r="W14" s="19"/>
     </row>
-    <row r="15" ht="15.75" customHeight="1">
+    <row r="15" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D15" s="19"/>
       <c r="E15" s="19"/>
@@ -4575,15 +4859,15 @@
       <c r="V15" s="19"/>
       <c r="W15" s="19"/>
     </row>
-    <row r="16" ht="15.75" customHeight="1">
+    <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D16" s="19"/>
       <c r="E16" s="19"/>
@@ -4606,7 +4890,7 @@
       <c r="V16" s="19"/>
       <c r="W16" s="19"/>
     </row>
-    <row r="17" ht="15.75" customHeight="1">
+    <row r="17" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="19"/>
       <c r="B17" s="19"/>
       <c r="C17" s="19"/>
@@ -4631,15 +4915,15 @@
       <c r="V17" s="19"/>
       <c r="W17" s="19"/>
     </row>
-    <row r="18" ht="15.75" customHeight="1">
+    <row r="18" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B18" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="C18" s="19" t="s">
         <v>101</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>103</v>
       </c>
       <c r="D18" s="19"/>
       <c r="E18" s="19"/>
@@ -4662,15 +4946,15 @@
       <c r="V18" s="19"/>
       <c r="W18" s="19"/>
     </row>
-    <row r="19" ht="15.75" customHeight="1">
+    <row r="19" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D19" s="19"/>
       <c r="E19" s="19"/>
@@ -4693,15 +4977,15 @@
       <c r="V19" s="19"/>
       <c r="W19" s="19"/>
     </row>
-    <row r="20" ht="15.75" customHeight="1">
+    <row r="20" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D20" s="19"/>
       <c r="E20" s="19"/>
@@ -4724,15 +5008,15 @@
       <c r="V20" s="19"/>
       <c r="W20" s="19"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
+    <row r="21" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D21" s="19"/>
       <c r="E21" s="19"/>
@@ -4755,15 +5039,15 @@
       <c r="V21" s="19"/>
       <c r="W21" s="19"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
+    <row r="22" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D22" s="19"/>
       <c r="E22" s="19"/>
@@ -4786,15 +5070,15 @@
       <c r="V22" s="19"/>
       <c r="W22" s="19"/>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
+    <row r="23" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="19" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
@@ -4817,7 +5101,7 @@
       <c r="V23" s="19"/>
       <c r="W23" s="19"/>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
+    <row r="24" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="19"/>
       <c r="B24" s="19"/>
       <c r="C24" s="19"/>
@@ -4842,15 +5126,15 @@
       <c r="V24" s="19"/>
       <c r="W24" s="19"/>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
+    <row r="25" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="C25" s="19" t="s">
         <v>121</v>
-      </c>
-      <c r="B25" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="C25" s="19" t="s">
-        <v>123</v>
       </c>
       <c r="D25" s="19"/>
       <c r="E25" s="19"/>
@@ -4873,15 +5157,15 @@
       <c r="V25" s="19"/>
       <c r="W25" s="19"/>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
+    <row r="26" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="19" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D26" s="19"/>
       <c r="E26" s="19"/>
@@ -4904,15 +5188,15 @@
       <c r="V26" s="19"/>
       <c r="W26" s="19"/>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
+    <row r="27" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="19" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D27" s="19"/>
       <c r="E27" s="19"/>
@@ -4935,15 +5219,15 @@
       <c r="V27" s="19"/>
       <c r="W27" s="19"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
+    <row r="28" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="19" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D28" s="19"/>
       <c r="E28" s="19"/>
@@ -4966,15 +5250,15 @@
       <c r="V28" s="19"/>
       <c r="W28" s="19"/>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
+    <row r="29" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D29" s="19"/>
       <c r="E29" s="19"/>
@@ -4997,7 +5281,7 @@
       <c r="V29" s="19"/>
       <c r="W29" s="19"/>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
+    <row r="30" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="19"/>
       <c r="B30" s="19"/>
       <c r="C30" s="19"/>
@@ -5022,15 +5306,15 @@
       <c r="V30" s="19"/>
       <c r="W30" s="19"/>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
+    <row r="31" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D31" s="19"/>
       <c r="E31" s="19"/>
@@ -5053,15 +5337,15 @@
       <c r="V31" s="19"/>
       <c r="W31" s="19"/>
     </row>
-    <row r="32" ht="15.75" customHeight="1">
+    <row r="32" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="B32" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="B32" s="19" t="s">
-        <v>137</v>
-      </c>
       <c r="C32" s="19" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D32" s="19"/>
       <c r="E32" s="19"/>
@@ -5084,7 +5368,7 @@
       <c r="V32" s="19"/>
       <c r="W32" s="19"/>
     </row>
-    <row r="33" ht="15.75" customHeight="1">
+    <row r="33" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="19"/>
       <c r="B33" s="19"/>
       <c r="C33" s="19"/>
@@ -5109,164 +5393,164 @@
       <c r="V33" s="19"/>
       <c r="W33" s="19"/>
     </row>
-    <row r="34" ht="15.75" customHeight="1">
+    <row r="34" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B34" t="str">
-        <f t="shared" ref="B34:B42" si="1">SUBSTITUTE(LOWER(SUBSTITUTE(SUBSTITUTE(C34, "(", ""), ")", "")), " ", "_")</f>
+        <f t="shared" ref="B34:B42" si="0">SUBSTITUTE(LOWER(SUBSTITUTE(SUBSTITUTE(C34, "(", ""), ")", "")), " ", "_")</f>
         <v>combined_oral_contraceptives</v>
       </c>
       <c r="C34" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>136</v>
+      </c>
+      <c r="B35" t="str">
+        <f t="shared" si="0"/>
+        <v>progesterone_only_pills</v>
+      </c>
+      <c r="C35" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>136</v>
+      </c>
+      <c r="B36" t="str">
+        <f t="shared" si="0"/>
+        <v>injectibles</v>
+      </c>
+      <c r="C36" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" t="s">
-        <v>138</v>
-      </c>
-      <c r="B35" t="str">
+    <row r="37" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>136</v>
+      </c>
+      <c r="B37" t="str">
+        <f t="shared" si="0"/>
+        <v>implants_1_rod</v>
+      </c>
+      <c r="C37" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>136</v>
+      </c>
+      <c r="B38" t="str">
+        <f t="shared" si="0"/>
+        <v>implants_2_rods</v>
+      </c>
+      <c r="C38" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>136</v>
+      </c>
+      <c r="B39" t="str">
+        <f t="shared" si="0"/>
+        <v>iud</v>
+      </c>
+      <c r="C39" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>136</v>
+      </c>
+      <c r="B40" t="str">
+        <f t="shared" si="0"/>
+        <v>condoms</v>
+      </c>
+      <c r="C40" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>136</v>
+      </c>
+      <c r="B41" t="str">
+        <f t="shared" si="0"/>
+        <v>tubal_ligation</v>
+      </c>
+      <c r="C41" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>136</v>
+      </c>
+      <c r="B42" t="str">
+        <f t="shared" si="0"/>
+        <v>cycle_beads</v>
+      </c>
+      <c r="C42" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>136</v>
+      </c>
+      <c r="B43" t="s">
+        <v>131</v>
+      </c>
+      <c r="C43" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" t="str">
+        <f t="shared" ref="B44:B47" si="1">SUBSTITUTE(LOWER(SUBSTITUTE(SUBSTITUTE(C44, "(", ""), ")", "")), " ", "_")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>157</v>
+      </c>
+      <c r="B45" t="str">
         <f t="shared" si="1"/>
-        <v>progesterone_only_pills</v>
-      </c>
-      <c r="C35" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" t="s">
-        <v>138</v>
-      </c>
-      <c r="B36" t="str">
+        <v>wants_to_get_pregnant</v>
+      </c>
+      <c r="C45" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>157</v>
+      </c>
+      <c r="B46" t="str">
         <f t="shared" si="1"/>
-        <v>injectibles</v>
-      </c>
-      <c r="C36" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" t="s">
-        <v>138</v>
-      </c>
-      <c r="B37" t="str">
+        <v>did_not_want_fp</v>
+      </c>
+      <c r="C46" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B47" t="str">
         <f t="shared" si="1"/>
-        <v>implants_1_rod</v>
-      </c>
-      <c r="C37" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" t="s">
-        <v>138</v>
-      </c>
-      <c r="B38" t="str">
-        <f t="shared" si="1"/>
-        <v>implants_2_rods</v>
-      </c>
-      <c r="C38" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" t="s">
-        <v>138</v>
-      </c>
-      <c r="B39" t="str">
-        <f t="shared" si="1"/>
-        <v>iud</v>
-      </c>
-      <c r="C39" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" t="s">
-        <v>138</v>
-      </c>
-      <c r="B40" t="str">
-        <f t="shared" si="1"/>
-        <v>condoms</v>
-      </c>
-      <c r="C40" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" t="s">
-        <v>138</v>
-      </c>
-      <c r="B41" t="str">
-        <f t="shared" si="1"/>
-        <v>tubal_ligation</v>
-      </c>
-      <c r="C41" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" t="s">
-        <v>138</v>
-      </c>
-      <c r="B42" t="str">
-        <f t="shared" si="1"/>
-        <v>cycle_beads</v>
-      </c>
-      <c r="C42" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" t="s">
-        <v>138</v>
-      </c>
-      <c r="B43" t="s">
-        <v>133</v>
-      </c>
-      <c r="C43" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="44" ht="15.75" customHeight="1">
-      <c r="B44" t="str">
-        <f t="shared" ref="B44:B47" si="2">SUBSTITUTE(LOWER(SUBSTITUTE(SUBSTITUTE(C44, "(", ""), ")", "")), " ", "_")</f>
         <v/>
       </c>
     </row>
-    <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" t="s">
-        <v>159</v>
-      </c>
-      <c r="B45" t="str">
-        <f t="shared" si="2"/>
-        <v>wants_to_get_pregnant</v>
-      </c>
-      <c r="C45" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" t="s">
-        <v>159</v>
-      </c>
-      <c r="B46" t="str">
-        <f t="shared" si="2"/>
-        <v>did_not_want_fp</v>
-      </c>
-      <c r="C46" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="47" ht="15.75" customHeight="1">
-      <c r="B47" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="15.75" customHeight="1">
+    <row r="48" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="24" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B48" s="24" t="s">
         <v>46</v>
@@ -5295,9 +5579,9 @@
       <c r="V48" s="13"/>
       <c r="W48" s="13"/>
     </row>
-    <row r="49" ht="15.75" customHeight="1">
+    <row r="49" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="24" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B49" s="24" t="s">
         <v>51</v>
@@ -5326,1158 +5610,1158 @@
       <c r="V49" s="13"/>
       <c r="W49" s="13"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1"/>
-    <row r="51" ht="15.75" customHeight="1">
+    <row r="50" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>166</v>
+      </c>
+      <c r="B51" t="s">
+        <v>167</v>
+      </c>
+      <c r="C51" t="s">
         <v>168</v>
       </c>
-      <c r="B51" t="s">
+    </row>
+    <row r="52" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>166</v>
+      </c>
+      <c r="B52" t="s">
         <v>169</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C52" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" t="s">
-        <v>168</v>
-      </c>
-      <c r="B52" t="s">
+    <row r="53" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>166</v>
+      </c>
+      <c r="B53" t="s">
         <v>171</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C53" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" t="s">
-        <v>168</v>
-      </c>
-      <c r="B53" t="s">
+    <row r="54" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>166</v>
+      </c>
+      <c r="B54" t="s">
         <v>173</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C54" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" t="s">
-        <v>168</v>
-      </c>
-      <c r="B54" t="s">
+    <row r="55" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>166</v>
+      </c>
+      <c r="B55" t="s">
         <v>175</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C55" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" t="s">
-        <v>168</v>
-      </c>
-      <c r="B55" t="s">
+    <row r="56" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>166</v>
+      </c>
+      <c r="B56" t="s">
+        <v>131</v>
+      </c>
+      <c r="C56" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="57" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="24" t="s">
         <v>177</v>
       </c>
-      <c r="C55" t="s">
+      <c r="B58" s="24" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" t="s">
-        <v>168</v>
-      </c>
-      <c r="B56" t="s">
-        <v>133</v>
-      </c>
-      <c r="C56" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="57" ht="15.75" customHeight="1"/>
-    <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="24" t="s">
+      <c r="C58" s="24" t="s">
         <v>179</v>
       </c>
-      <c r="B58" s="24" t="s">
+    </row>
+    <row r="59" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="B59" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="C58" s="24" t="s">
+      <c r="C59" s="24" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="24" t="s">
-        <v>179</v>
-      </c>
-      <c r="B59" s="24" t="s">
+    <row r="60" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="B60" s="24" t="s">
         <v>182</v>
       </c>
-      <c r="C59" s="24" t="s">
+      <c r="C60" s="24" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="24" t="s">
-        <v>179</v>
-      </c>
-      <c r="B60" s="24" t="s">
-        <v>184</v>
-      </c>
-      <c r="C60" s="24" t="s">
+    <row r="61" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="B61" s="24" t="s">
+        <v>131</v>
+      </c>
+      <c r="C61" s="24" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="62" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="13" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="24" t="s">
-        <v>179</v>
-      </c>
-      <c r="B61" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="C61" s="24" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="62" ht="15.75" customHeight="1"/>
-    <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="13" t="s">
+      <c r="B63" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="C63" s="24" t="s">
         <v>187</v>
       </c>
-      <c r="B63" s="13" t="s">
+    </row>
+    <row r="64" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="B64" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="C63" s="24" t="s">
+      <c r="C64" s="24" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="B64" s="13" t="s">
-        <v>190</v>
-      </c>
-      <c r="C64" s="24" t="s">
+    <row r="65" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="B65" s="13" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="B65" s="13" t="s">
+      <c r="C65" s="24" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="B66" s="13" t="s">
         <v>193</v>
       </c>
-      <c r="C65" s="24" t="s">
+      <c r="C66" s="24" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="B66" s="13" t="s">
+    <row r="67" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="B67" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="C66" s="24" t="s">
+      <c r="C67" s="24" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="B67" s="13" t="s">
+    <row r="68" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
         <v>197</v>
       </c>
-      <c r="C67" s="24" t="s">
+      <c r="B69" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="68" ht="15.75" customHeight="1"/>
-    <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" t="s">
+      <c r="C69" t="s">
         <v>199</v>
       </c>
-      <c r="B69" t="s">
+    </row>
+    <row r="70" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>197</v>
+      </c>
+      <c r="B70" t="s">
         <v>200</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C70" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" t="s">
-        <v>199</v>
-      </c>
-      <c r="B70" t="s">
+    <row r="71" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
         <v>202</v>
       </c>
-      <c r="C70" t="s">
+      <c r="B72" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="71" ht="15.75" customHeight="1"/>
-    <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" t="s">
+      <c r="C72" s="46" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>202</v>
+      </c>
+      <c r="B73" t="s">
         <v>204</v>
       </c>
-      <c r="B72" t="s">
+      <c r="C73" t="s">
         <v>205</v>
       </c>
-      <c r="C72" s="46" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" t="s">
-        <v>204</v>
-      </c>
-      <c r="B73" t="s">
-        <v>206</v>
-      </c>
-      <c r="C73" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="74" ht="15.75" customHeight="1">
+    </row>
+    <row r="74" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B74" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C74" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="75" ht="15.75" customHeight="1"/>
-    <row r="76" ht="15.75" customHeight="1"/>
-    <row r="77" ht="15.75" customHeight="1"/>
-    <row r="78" ht="15.75" customHeight="1"/>
-    <row r="79" ht="15.75" customHeight="1"/>
-    <row r="80" ht="15.75" customHeight="1"/>
-    <row r="81" ht="15.75" customHeight="1"/>
-    <row r="82" ht="15.75" customHeight="1"/>
-    <row r="83" ht="15.75" customHeight="1"/>
-    <row r="84" ht="15.75" customHeight="1"/>
-    <row r="85" ht="15.75" customHeight="1"/>
-    <row r="86" ht="15.75" customHeight="1"/>
-    <row r="87" ht="15.75" customHeight="1"/>
-    <row r="88" ht="15.75" customHeight="1"/>
-    <row r="89" ht="15.75" customHeight="1"/>
-    <row r="90" ht="15.75" customHeight="1"/>
-    <row r="91" ht="15.75" customHeight="1"/>
-    <row r="92" ht="15.75" customHeight="1"/>
-    <row r="93" ht="15.75" customHeight="1"/>
-    <row r="94" ht="15.75" customHeight="1"/>
-    <row r="95" ht="15.75" customHeight="1"/>
-    <row r="96" ht="15.75" customHeight="1"/>
-    <row r="97" ht="15.75" customHeight="1"/>
-    <row r="98" ht="15.75" customHeight="1"/>
-    <row r="99" ht="15.75" customHeight="1"/>
-    <row r="100" ht="15.75" customHeight="1"/>
-    <row r="101" ht="15.75" customHeight="1"/>
-    <row r="102" ht="15.75" customHeight="1"/>
-    <row r="103" ht="15.75" customHeight="1"/>
-    <row r="104" ht="15.75" customHeight="1"/>
-    <row r="105" ht="15.75" customHeight="1"/>
-    <row r="106" ht="15.75" customHeight="1"/>
-    <row r="107" ht="15.75" customHeight="1"/>
-    <row r="108" ht="15.75" customHeight="1"/>
-    <row r="109" ht="15.75" customHeight="1"/>
-    <row r="110" ht="15.75" customHeight="1"/>
-    <row r="111" ht="15.75" customHeight="1"/>
-    <row r="112" ht="15.75" customHeight="1"/>
-    <row r="113" ht="15.75" customHeight="1"/>
-    <row r="114" ht="15.75" customHeight="1"/>
-    <row r="115" ht="15.75" customHeight="1"/>
-    <row r="116" ht="15.75" customHeight="1"/>
-    <row r="117" ht="15.75" customHeight="1"/>
-    <row r="118" ht="15.75" customHeight="1"/>
-    <row r="119" ht="15.75" customHeight="1"/>
-    <row r="120" ht="15.75" customHeight="1"/>
-    <row r="121" ht="15.75" customHeight="1"/>
-    <row r="122" ht="15.75" customHeight="1"/>
-    <row r="123" ht="15.75" customHeight="1"/>
-    <row r="124" ht="15.75" customHeight="1"/>
-    <row r="125" ht="15.75" customHeight="1"/>
-    <row r="126" ht="15.75" customHeight="1"/>
-    <row r="127" ht="15.75" customHeight="1"/>
-    <row r="128" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
-    <row r="193" ht="15.75" customHeight="1"/>
-    <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
-    <row r="809" ht="15.75" customHeight="1"/>
-    <row r="810" ht="15.75" customHeight="1"/>
-    <row r="811" ht="15.75" customHeight="1"/>
-    <row r="812" ht="15.75" customHeight="1"/>
-    <row r="813" ht="15.75" customHeight="1"/>
-    <row r="814" ht="15.75" customHeight="1"/>
-    <row r="815" ht="15.75" customHeight="1"/>
-    <row r="816" ht="15.75" customHeight="1"/>
-    <row r="817" ht="15.75" customHeight="1"/>
-    <row r="818" ht="15.75" customHeight="1"/>
-    <row r="819" ht="15.75" customHeight="1"/>
-    <row r="820" ht="15.75" customHeight="1"/>
-    <row r="821" ht="15.75" customHeight="1"/>
-    <row r="822" ht="15.75" customHeight="1"/>
-    <row r="823" ht="15.75" customHeight="1"/>
-    <row r="824" ht="15.75" customHeight="1"/>
-    <row r="825" ht="15.75" customHeight="1"/>
-    <row r="826" ht="15.75" customHeight="1"/>
-    <row r="827" ht="15.75" customHeight="1"/>
-    <row r="828" ht="15.75" customHeight="1"/>
-    <row r="829" ht="15.75" customHeight="1"/>
-    <row r="830" ht="15.75" customHeight="1"/>
-    <row r="831" ht="15.75" customHeight="1"/>
-    <row r="832" ht="15.75" customHeight="1"/>
-    <row r="833" ht="15.75" customHeight="1"/>
-    <row r="834" ht="15.75" customHeight="1"/>
-    <row r="835" ht="15.75" customHeight="1"/>
-    <row r="836" ht="15.75" customHeight="1"/>
-    <row r="837" ht="15.75" customHeight="1"/>
-    <row r="838" ht="15.75" customHeight="1"/>
-    <row r="839" ht="15.75" customHeight="1"/>
-    <row r="840" ht="15.75" customHeight="1"/>
-    <row r="841" ht="15.75" customHeight="1"/>
-    <row r="842" ht="15.75" customHeight="1"/>
-    <row r="843" ht="15.75" customHeight="1"/>
-    <row r="844" ht="15.75" customHeight="1"/>
-    <row r="845" ht="15.75" customHeight="1"/>
-    <row r="846" ht="15.75" customHeight="1"/>
-    <row r="847" ht="15.75" customHeight="1"/>
-    <row r="848" ht="15.75" customHeight="1"/>
-    <row r="849" ht="15.75" customHeight="1"/>
-    <row r="850" ht="15.75" customHeight="1"/>
-    <row r="851" ht="15.75" customHeight="1"/>
-    <row r="852" ht="15.75" customHeight="1"/>
-    <row r="853" ht="15.75" customHeight="1"/>
-    <row r="854" ht="15.75" customHeight="1"/>
-    <row r="855" ht="15.75" customHeight="1"/>
-    <row r="856" ht="15.75" customHeight="1"/>
-    <row r="857" ht="15.75" customHeight="1"/>
-    <row r="858" ht="15.75" customHeight="1"/>
-    <row r="859" ht="15.75" customHeight="1"/>
-    <row r="860" ht="15.75" customHeight="1"/>
-    <row r="861" ht="15.75" customHeight="1"/>
-    <row r="862" ht="15.75" customHeight="1"/>
-    <row r="863" ht="15.75" customHeight="1"/>
-    <row r="864" ht="15.75" customHeight="1"/>
-    <row r="865" ht="15.75" customHeight="1"/>
-    <row r="866" ht="15.75" customHeight="1"/>
-    <row r="867" ht="15.75" customHeight="1"/>
-    <row r="868" ht="15.75" customHeight="1"/>
-    <row r="869" ht="15.75" customHeight="1"/>
-    <row r="870" ht="15.75" customHeight="1"/>
-    <row r="871" ht="15.75" customHeight="1"/>
-    <row r="872" ht="15.75" customHeight="1"/>
-    <row r="873" ht="15.75" customHeight="1"/>
-    <row r="874" ht="15.75" customHeight="1"/>
-    <row r="875" ht="15.75" customHeight="1"/>
-    <row r="876" ht="15.75" customHeight="1"/>
-    <row r="877" ht="15.75" customHeight="1"/>
-    <row r="878" ht="15.75" customHeight="1"/>
-    <row r="879" ht="15.75" customHeight="1"/>
-    <row r="880" ht="15.75" customHeight="1"/>
-    <row r="881" ht="15.75" customHeight="1"/>
-    <row r="882" ht="15.75" customHeight="1"/>
-    <row r="883" ht="15.75" customHeight="1"/>
-    <row r="884" ht="15.75" customHeight="1"/>
-    <row r="885" ht="15.75" customHeight="1"/>
-    <row r="886" ht="15.75" customHeight="1"/>
-    <row r="887" ht="15.75" customHeight="1"/>
-    <row r="888" ht="15.75" customHeight="1"/>
-    <row r="889" ht="15.75" customHeight="1"/>
-    <row r="890" ht="15.75" customHeight="1"/>
-    <row r="891" ht="15.75" customHeight="1"/>
-    <row r="892" ht="15.75" customHeight="1"/>
-    <row r="893" ht="15.75" customHeight="1"/>
-    <row r="894" ht="15.75" customHeight="1"/>
-    <row r="895" ht="15.75" customHeight="1"/>
-    <row r="896" ht="15.75" customHeight="1"/>
-    <row r="897" ht="15.75" customHeight="1"/>
-    <row r="898" ht="15.75" customHeight="1"/>
-    <row r="899" ht="15.75" customHeight="1"/>
-    <row r="900" ht="15.75" customHeight="1"/>
-    <row r="901" ht="15.75" customHeight="1"/>
-    <row r="902" ht="15.75" customHeight="1"/>
-    <row r="903" ht="15.75" customHeight="1"/>
-    <row r="904" ht="15.75" customHeight="1"/>
-    <row r="905" ht="15.75" customHeight="1"/>
-    <row r="906" ht="15.75" customHeight="1"/>
-    <row r="907" ht="15.75" customHeight="1"/>
-    <row r="908" ht="15.75" customHeight="1"/>
-    <row r="909" ht="15.75" customHeight="1"/>
-    <row r="910" ht="15.75" customHeight="1"/>
-    <row r="911" ht="15.75" customHeight="1"/>
-    <row r="912" ht="15.75" customHeight="1"/>
-    <row r="913" ht="15.75" customHeight="1"/>
-    <row r="914" ht="15.75" customHeight="1"/>
-    <row r="915" ht="15.75" customHeight="1"/>
-    <row r="916" ht="15.75" customHeight="1"/>
-    <row r="917" ht="15.75" customHeight="1"/>
-    <row r="918" ht="15.75" customHeight="1"/>
-    <row r="919" ht="15.75" customHeight="1"/>
-    <row r="920" ht="15.75" customHeight="1"/>
-    <row r="921" ht="15.75" customHeight="1"/>
-    <row r="922" ht="15.75" customHeight="1"/>
-    <row r="923" ht="15.75" customHeight="1"/>
-    <row r="924" ht="15.75" customHeight="1"/>
-    <row r="925" ht="15.75" customHeight="1"/>
-    <row r="926" ht="15.75" customHeight="1"/>
-    <row r="927" ht="15.75" customHeight="1"/>
-    <row r="928" ht="15.75" customHeight="1"/>
-    <row r="929" ht="15.75" customHeight="1"/>
-    <row r="930" ht="15.75" customHeight="1"/>
-    <row r="931" ht="15.75" customHeight="1"/>
-    <row r="932" ht="15.75" customHeight="1"/>
-    <row r="933" ht="15.75" customHeight="1"/>
-    <row r="934" ht="15.75" customHeight="1"/>
-    <row r="935" ht="15.75" customHeight="1"/>
-    <row r="936" ht="15.75" customHeight="1"/>
-    <row r="937" ht="15.75" customHeight="1"/>
-    <row r="938" ht="15.75" customHeight="1"/>
-    <row r="939" ht="15.75" customHeight="1"/>
-    <row r="940" ht="15.75" customHeight="1"/>
-    <row r="941" ht="15.75" customHeight="1"/>
-    <row r="942" ht="15.75" customHeight="1"/>
-    <row r="943" ht="15.75" customHeight="1"/>
-    <row r="944" ht="15.75" customHeight="1"/>
-    <row r="945" ht="15.75" customHeight="1"/>
-    <row r="946" ht="15.75" customHeight="1"/>
-    <row r="947" ht="15.75" customHeight="1"/>
-    <row r="948" ht="15.75" customHeight="1"/>
-    <row r="949" ht="15.75" customHeight="1"/>
-    <row r="950" ht="15.75" customHeight="1"/>
-    <row r="951" ht="15.75" customHeight="1"/>
-    <row r="952" ht="15.75" customHeight="1"/>
-    <row r="953" ht="15.75" customHeight="1"/>
-    <row r="954" ht="15.75" customHeight="1"/>
-    <row r="955" ht="15.75" customHeight="1"/>
-    <row r="956" ht="15.75" customHeight="1"/>
-    <row r="957" ht="15.75" customHeight="1"/>
-    <row r="958" ht="15.75" customHeight="1"/>
-    <row r="959" ht="15.75" customHeight="1"/>
-    <row r="960" ht="15.75" customHeight="1"/>
-    <row r="961" ht="15.75" customHeight="1"/>
-    <row r="962" ht="15.75" customHeight="1"/>
-    <row r="963" ht="15.75" customHeight="1"/>
-    <row r="964" ht="15.75" customHeight="1"/>
-    <row r="965" ht="15.75" customHeight="1"/>
-    <row r="966" ht="15.75" customHeight="1"/>
-    <row r="967" ht="15.75" customHeight="1"/>
-    <row r="968" ht="15.75" customHeight="1"/>
-    <row r="969" ht="15.75" customHeight="1"/>
-    <row r="970" ht="15.75" customHeight="1"/>
-    <row r="971" ht="15.75" customHeight="1"/>
-    <row r="972" ht="15.75" customHeight="1"/>
-    <row r="973" ht="15.75" customHeight="1"/>
-    <row r="974" ht="15.75" customHeight="1"/>
-    <row r="975" ht="15.75" customHeight="1"/>
-    <row r="976" ht="15.75" customHeight="1"/>
-    <row r="977" ht="15.75" customHeight="1"/>
-    <row r="978" ht="15.75" customHeight="1"/>
-    <row r="979" ht="15.75" customHeight="1"/>
-    <row r="980" ht="15.75" customHeight="1"/>
-    <row r="981" ht="15.75" customHeight="1"/>
-    <row r="982" ht="15.75" customHeight="1"/>
-    <row r="983" ht="15.75" customHeight="1"/>
-    <row r="984" ht="15.75" customHeight="1"/>
-    <row r="985" ht="15.75" customHeight="1"/>
-    <row r="986" ht="15.75" customHeight="1"/>
-    <row r="987" ht="15.75" customHeight="1"/>
-    <row r="988" ht="15.75" customHeight="1"/>
-    <row r="989" ht="15.75" customHeight="1"/>
-    <row r="990" ht="15.75" customHeight="1"/>
-    <row r="991" ht="15.75" customHeight="1"/>
-    <row r="992" ht="15.75" customHeight="1"/>
-    <row r="993" ht="15.75" customHeight="1"/>
-    <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
+        <v>132</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>